--- a/systeme_de_Classification_Intelligent_des_emails/emails_output/emails.xlsx
+++ b/systeme_de_Classification_Intelligent_des_emails/emails_output/emails.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>UID</t>
   </si>
@@ -25,30 +25,52 @@
     <t>Attachments</t>
   </si>
   <si>
-    <t xml:space="preserve">---------- Forwarded message ---------_x000D_
-From: yessine tony &lt;yessinetony@gmail.com&gt;_x000D_
-Date: Mon, 6 Apr 2026 at 10:22_x000D_
-Subject: nigga_x000D_
-To: Yessineht@gmail.com &lt;Yessineht@gmail.com&gt;_x000D_
+    <t>19</t>
+  </si>
+  <si>
+    <t>---------- Forwarded message ---------_x005F_x000D_
+From: yessine tony &lt;yessinetony@gmail.com&gt;_x005F_x000D_
+Date: Mon, 6 Apr 2026 at 10:22_x005F_x000D_
+Subject: nigga_x005F_x000D_
+To: Yessineht@gmail.com &lt;Yessineht@gmail.com&gt;_x005F_x000D_
+_x005F_x000D_
+_x005F_x000D_
+this is a test for the attatchement</t>
+  </si>
+  <si>
+    <t>Yessine Ht &lt;yessineht@gmail.com&gt;
+Bonjour,_x000D_
 _x000D_
+Je vous écris afin de vous demander l’autorisation de prendre un congé._x000D_
 _x000D_
-this is a test for the attatchement</t>
+Durant cette période, je veillerai à ce que toutes mes tâches en cours_x000D_
+soient organisées ou transmises afin d’assurer la continuité du travail._x000D_
+_x000D_
+Je reste bien entendu disponible pour toute information complémentaire et_x000D_
+je vous remercie par avance pour votre compréhension._x000D_
+_x000D_
+Cordialement,_x000D_
+yessine haj taieb_x000D_
+developpeur</t>
   </si>
   <si>
     <t>Rapport.pdf; Asset 11.png</t>
+  </si>
+  <si>
+    <t>Doctor_Note_with_Signature.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -78,15 +100,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -374,11 +388,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -389,19 +403,28 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/systeme_de_Classification_Intelligent_des_emails/emails_output/emails.xlsx
+++ b/systeme_de_Classification_Intelligent_des_emails/emails_output/emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>UID</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Attachments</t>
   </si>
   <si>
-    <t>19</t>
+    <t>30</t>
   </si>
   <si>
     <t>---------- Forwarded message ---------_x005F_x000D_
@@ -39,25 +39,68 @@
   </si>
   <si>
     <t>Yessine Ht &lt;yessineht@gmail.com&gt;
-Bonjour,_x000D_
+Bonjour,_x005F_x000D_
+_x005F_x000D_
+Je vous écris afin de vous demander l’autorisation de prendre un congé._x005F_x000D_
+_x005F_x000D_
+Durant cette période, je veillerai à ce que toutes mes tâches en cours_x005F_x000D_
+soient organisées ou transmises afin d’assurer la continuité du travail._x005F_x000D_
+_x005F_x000D_
+Je reste bien entendu disponible pour toute information complémentaire et_x005F_x000D_
+je vous remercie par avance pour votre compréhension._x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
+yessine haj taieb_x005F_x000D_
+developpeur</t>
+  </si>
+  <si>
+    <t>Yessine Ht &lt;yessineht@gmail.com&gt;
+Bonjour,_x005F_x000D_
+Je rencontre actuellement un problème lors de l’accès à mon espace client._x005F_x000D_
+En effet, l’application affiche une erreur 404, ce qui m’empêche d’y_x005F_x000D_
+accéder. Je ne comprends pas l’origine de ce problème et je vous serais_x005F_x000D_
+reconnaissant de bien vouloir m’aider à le résoudre dans les plus brefs_x005F_x000D_
+délais. Je reste à votre disposition pour toute information complémentaire._x005F_x000D_
+Cordialement,_x005F_x000D_
+yessine Haj Taieb_x005F_x000D_
+[image: image.png]</t>
+  </si>
+  <si>
+    <t>From: Yessine Ht &lt;yessineht@gmail.com&gt; 
+ Subject: Mission Order Request 
+ Date: Fri, 15 May 2026 23:46:48 +0100 
+ Bonjour,_x000D_
 _x000D_
-Je vous écris afin de vous demander l’autorisation de prendre un congé._x000D_
+J'espère que vous allez bien ! Je me permets de vous contacter afin de_x000D_
+solliciter votre validation pour un court déplacement professionnel prévu_x000D_
+les 17 et 18 novembre 2024 à Kairouan. Cette mission est liée à des_x000D_
+activités en cours qui nécessitent vraiment une présence sur place, et je_x000D_
+souhaite m'assurer que tout se passe dans les meilleures conditions._x000D_
 _x000D_
-Durant cette période, je veillerai à ce que toutes mes tâches en cours_x000D_
-soient organisées ou transmises afin d’assurer la continuité du travail._x000D_
+Voici mes informations pour la demande : je m'appelle Imen Souissi, vous_x000D_
+pouvez me joindre à l'adresse imen.souissi@hrtech-solutions.tn, et la_x000D_
+destination est Kairouan pour ces deux journées. L'accord de mon_x000D_
+responsable est encore en attente, mais je souhaitais vous transmettre_x000D_
+cette demande en avance afin d'éviter tout délai de traitement._x000D_
 _x000D_
-Je reste bien entendu disponible pour toute information complémentaire et_x000D_
-je vous remercie par avance pour votre compréhension._x000D_
+Si vous avez besoin de quoi que ce soit de ma part — documents_x000D_
+supplémentaires, détails sur les objectifs de la mission, ou autre —_x000D_
+n'hésitez pas à me le faire savoir et je vous fournirai tout cela dans les_x000D_
+plus brefs délais._x000D_
+_x000D_
+Merci beaucoup pour votre aide et votre disponibilité !_x000D_
 _x000D_
 Cordialement,_x000D_
-yessine haj taieb_x000D_
-developpeur</t>
+yessine haj taieb</t>
   </si>
   <si>
     <t>Rapport.pdf; Asset 11.png</t>
   </si>
   <si>
     <t>Doctor_Note_with_Signature.pdf</t>
+  </si>
+  <si>
+    <t>image.png</t>
   </si>
 </sst>
 </file>
@@ -389,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -411,17 +454,36 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
+      <c r="A3">
+        <v>19</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>7</v>
       </c>
     </row>

--- a/systeme_de_Classification_Intelligent_des_emails/emails_output/emails.xlsx
+++ b/systeme_de_Classification_Intelligent_des_emails/emails_output/emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>UID</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Attachments</t>
   </si>
   <si>
-    <t>30</t>
+    <t>35</t>
   </si>
   <si>
     <t>---------- Forwarded message ---------_x005F_x000D_
@@ -69,29 +69,240 @@
     <t>From: Yessine Ht &lt;yessineht@gmail.com&gt; 
  Subject: Mission Order Request 
  Date: Fri, 15 May 2026 23:46:48 +0100 
- Bonjour,_x000D_
+ Bonjour,_x005F_x000D_
+_x005F_x000D_
+J'espère que vous allez bien ! Je me permets de vous contacter afin de_x005F_x000D_
+solliciter votre validation pour un court déplacement professionnel prévu_x005F_x000D_
+les 17 et 18 novembre 2024 à Kairouan. Cette mission est liée à des_x005F_x000D_
+activités en cours qui nécessitent vraiment une présence sur place, et je_x005F_x000D_
+souhaite m'assurer que tout se passe dans les meilleures conditions._x005F_x000D_
+_x005F_x000D_
+Voici mes informations pour la demande : je m'appelle Imen Souissi, vous_x005F_x000D_
+pouvez me joindre à l'adresse imen.souissi@hrtech-solutions.tn, et la_x005F_x000D_
+destination est Kairouan pour ces deux journées. L'accord de mon_x005F_x000D_
+responsable est encore en attente, mais je souhaitais vous transmettre_x005F_x000D_
+cette demande en avance afin d'éviter tout délai de traitement._x005F_x000D_
+_x005F_x000D_
+Si vous avez besoin de quoi que ce soit de ma part — documents_x005F_x000D_
+supplémentaires, détails sur les objectifs de la mission, ou autre —_x005F_x000D_
+n'hésitez pas à me le faire savoir et je vous fournirai tout cela dans les_x005F_x000D_
+plus brefs délais._x005F_x000D_
+_x005F_x000D_
+Merci beaucoup pour votre aide et votre disponibilité !_x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
+yessine haj taieb</t>
+  </si>
+  <si>
+    <t>From: Yessine Ht &lt;yessineht@gmail.com&gt; 
+ Subject: Mission Order Request 
+ Date: Tue, 19 May 2026 21:42:45 +0100 
+ J'espère que vous allez bien ! Je me permets de vous contacter afin de_x005F_x000D_
+solliciter votre validation pour un court déplacement professionnel prévu_x005F_x000D_
+les 17 et 18 novembre 2024 à Kairouan. Cette mission est liée à des_x005F_x000D_
+activités en cours qui nécessitent vraiment une présence sur place, et je_x005F_x000D_
+souhaite m'assurer que tout se passe dans les meilleures conditions._x005F_x000D_
+_x005F_x000D_
+Voici mes informations pour la demande : je m'appelle Imen Souissi, vous_x005F_x000D_
+pouvez me joindre à l'adresse yessineht@gmail.com, et la destination est_x005F_x000D_
+Kairouan pour ces deux journées. L'accord de mon responsable est encore en_x005F_x000D_
+attente, mais je souhaitais vous transmettre cette demande en avance afin_x005F_x000D_
+d'éviter tout délai de traitement._x005F_x000D_
+_x005F_x000D_
+Si vous avez besoin de quoi que ce soit de ma part — documents_x005F_x000D_
+supplémentaires, détails sur les objectifs de la mission, ou autre —_x005F_x000D_
+n'hésitez pas à me le faire savoir et je vous fournirai tout cela dans les_x005F_x000D_
+plus brefs délais._x005F_x000D_
+_x005F_x000D_
+Merci beaucoup pour votre aide et votre disponibilité !_x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
+yessine haj taieb</t>
+  </si>
+  <si>
+    <t>From: Yessine Ht &lt;yessineht@gmail.com&gt; 
+ Subject: Demande de recrutement – Poste : Développeur Full Stack 
+ Date: Thu, 21 May 2026 09:45:19 +0100 
+ Madame, Monsieur,_x005F_x000D_
+_x005F_x000D_
+Je me permets de vous adresser la présente afin d'initier une demande de_x005F_x000D_
+recrutement pour le poste de Développeur Full Stack au sein de notre_x005F_x000D_
+département Informatique._x005F_x000D_
+_x005F_x000D_
+**Description du besoin**_x005F_x000D_
+Face à l'accroissement de nos projets de développement, nous avons besoin_x005F_x000D_
+de renforcer notre équipe technique par le recrutement d'un profil_x005F_x000D_
+expérimenté en développement web Full Stack._x005F_x000D_
+_x005F_x000D_
+**Poste**_x005F_x000D_
+Développeur Full Stack_x005F_x000D_
+_x005F_x000D_
+**Documents joints**_x005F_x000D_
+- Fiche de poste : ci-jointe_x005F_x000D_
+- Questionnaire de recrutement : ci-joint_x005F_x000D_
+_x005F_x000D_
+**Présélection des candidats**_x005F_x000D_
+Suite à l'analyse des candidatures reçues, les candidats présélectionnés_x005F_x000D_
+sont les suivants :_x005F_x000D_
+1. Ahmed Ben Salem_x005F_x000D_
+2. Sonia Trabelsi_x005F_x000D_
+3. Karim Mansour_x005F_x000D_
+_x005F_x000D_
+**Entretien(s)**_x005F_x000D_
+- Date d'entretien : 28/05/2026_x005F_x000D_
+- Type d'entretien : Entretien technique + RH_x005F_x000D_
+- Évaluateurs : M. Youssef Chaabane (Responsable technique), Mme Rim_x005F_x000D_
+Bouaziz (RH)_x005F_x000D_
+_x005F_x000D_
+**Résultats**_x005F_x000D_
+- Résultats des questionnaires : ci-joints_x005F_x000D_
+- Résultat de l'entretien : Favorable pour M. Ahmed Ben Salem_x005F_x000D_
+_x005F_x000D_
+**Candidat retenu**_x005F_x000D_
+- Nom du candidat retenu : Ahmed Ben Salem_x005F_x000D_
+- Type de contrat : CDI_x005F_x000D_
+- Date d'embauche : 01/07/2026_x005F_x000D_
+- Seuil de proposition d'embauche : 2 800 TND_x005F_x000D_
+- Proposition finale d'embauche : 3 000 TND_x005F_x000D_
+_x005F_x000D_
+Nous vous prions de bien vouloir procéder à la préparation du contrat et de_x005F_x000D_
+planifier la signature dans les meilleurs délais._x005F_x000D_
+_x005F_x000D_
+Contrat : à établir_x005F_x000D_
+_x005F_x000D_
+Restant à votre disposition pour tout complément d'information,_x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
+_x005F_x000D_
+Mohamed Khalil_x005F_x000D_
+Responsable Département Informatique_x005F_x000D_
+m.khalil@entreprise.tn | +216 71 000 000</t>
+  </si>
+  <si>
+    <t>From: Yessine Ht &lt;yessineht@gmail.com&gt; 
+ Subject: Évaluation de fin de période d'essai – Mme Sonia Trabelsi 
+ Date: Thu, 21 May 2026 09:48:26 +0100 
+ Madame, Monsieur,_x005F_x000D_
+_x005F_x000D_
+Je vous transmets ci-dessous le rapport d'évaluation de fin de période_x005F_x000D_
+d'essai concernant Mme Sonia Trabelsi, intégrée au sein du département_x005F_x000D_
+Ressources Humaines depuis le 01/03/2026._x005F_x000D_
+_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+I. ÉVALUATION PAR LE SUPÉRIEUR HIÉRARCHIQUE_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+_x005F_x000D_
+Collaborateur évalué : Mme Sonia Trabelsi_x005F_x000D_
+Responsable évaluateur : M. Youssef Chaabane – Responsable RH_x005F_x000D_
+_x005F_x000D_
+• Connaissance de l'emploi : Bonne maîtrise des procédures internes et des_x005F_x000D_
+outils RH utilisés. S'est rapidement approprié les processus en place._x005F_x000D_
+_x005F_x000D_
+• Productivité (Qualité / Quantité de travail) : Travail soigné et livré_x005F_x000D_
+dans les délais impartis. Volume de tâches traitées conforme aux attentes_x005F_x000D_
+du poste._x005F_x000D_
+_x005F_x000D_
+• Fiabilité : Ponctuelle, rigoureuse et respectueuse de ses engagements._x005F_x000D_
+Aucune absence non justifiée durant la période d'essai._x005F_x000D_
+_x005F_x000D_
+• Collaboration : S'intègre facilement dans les dynamiques d'équipe._x005F_x000D_
+Participe activement aux réunions et contribue aux projets collectifs._x005F_x000D_
+_x005F_x000D_
+• Adaptabilité : A démontré une bonne capacité d'adaptation face aux_x005F_x000D_
+changements de priorités et aux situations imprévues._x005F_x000D_
+_x005F_x000D_
+• Initiative : Fait preuve d'empressement et de proactivité. A proposé_x005F_x000D_
+plusieurs améliorations sur les procédures de suivi des candidatures._x005F_x000D_
+_x005F_x000D_
+• Service à la clientèle / fournisseurs : Interactions professionnelles et_x005F_x000D_
+courtoises avec les partenaires externes et les candidats._x005F_x000D_
+_x005F_x000D_
+• Commentaire général : Mme Trabelsi est une collaboratrice sérieuse et_x005F_x000D_
+investie. Son intégration au sein de l'équipe s'est déroulée de manière_x005F_x000D_
+très satisfaisante._x005F_x000D_
+_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+II. ÉVALUATION RH_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+_x005F_x000D_
+• Attitudes et comportements au travail : Comportement exemplaire,_x005F_x000D_
+respectueux des valeurs et du règlement intérieur de l'entreprise._x005F_x000D_
+_x005F_x000D_
+• Motivation et satisfaction personnelle : Se déclare motivée par ses_x005F_x000D_
+missions et exprime un intérêt marqué pour évoluer au sein du département._x005F_x000D_
+_x005F_x000D_
+• Environnement de travail et organisation générale : S'est bien adaptée à_x005F_x000D_
+l'environnement de travail. Espace de travail organisé, gestion du temps_x005F_x000D_
+satisfaisante._x005F_x000D_
+_x005F_x000D_
+• Encadrement et intégration : L'accompagnement réalisé durant la période_x005F_x000D_
+d'essai a été jugé suffisant. La collaboratrice a bénéficié d'un suivi_x005F_x000D_
+régulier par son responsable direct._x005F_x000D_
+_x005F_x000D_
+• Écarts constatés : Légère marge de progression identifiée sur la gestion_x005F_x000D_
+des priorités en période de forte charge. Point à suivre lors du prochain_x005F_x000D_
+entretien annuel._x005F_x000D_
+_x005F_x000D_
+• Relation avec les collègues au sein du département : Excellentes_x005F_x000D_
+relations interpersonnelles. Appréciée par l'ensemble de l'équipe pour son_x005F_x000D_
+esprit d'entraide._x005F_x000D_
+_x005F_x000D_
+• Ambition exprimée : Souhaite à terme prendre en charge le volet formation_x005F_x000D_
+et développement des compétences au sein du département RH._x005F_x000D_
+_x005F_x000D_
+• Proposition d'amélioration : Nous recommandons de lui confier_x005F_x000D_
+progressivement des missions de coordination afin de développer ses_x005F_x000D_
+compétences managériales._x005F_x000D_
+_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+III. DÉCISION_x005F_x000D_
+━━━━━━━━━━━━━━━━━━━━━━━━_x005F_x000D_
+_x005F_x000D_
+• Décision proposée : Confirmation de la titularisation à l'issue de la_x005F_x000D_
+période d'essai._x005F_x000D_
+• Décision finale : FAVORABLE – Intégration définitive au sein du_x005F_x000D_
+département RH à compter du 01/06/2026._x005F_x000D_
+_x005F_x000D_
+Nous vous prions de bien vouloir prendre note de cette décision et de_x005F_x000D_
+procéder aux formalités administratives nécessaires à la confirmation du_x005F_x000D_
+contrat._x005F_x000D_
+_x005F_x000D_
+Restant à votre disposition pour tout complément d'information,_x005F_x000D_
+_x005F_x000D_
+Cordialement,_x005F_x000D_
+_x005F_x000D_
+Mme Rim Bouaziz_x005F_x000D_
+Chargée des Ressources Humaines_x005F_x000D_
+r.bouaziz@entreprise.tn | +216 71 000 001</t>
+  </si>
+  <si>
+    <t>From: Yessine Ht &lt;yessineht@gmail.com&gt; 
+ Subject: Demande d'autorisation d'absence – 27/05/2026 
+ Date: Thu, 21 May 2026 11:27:18 +0100 
+ Madame, Monsieur,_x000D_
 _x000D_
-J'espère que vous allez bien ! Je me permets de vous contacter afin de_x000D_
-solliciter votre validation pour un court déplacement professionnel prévu_x000D_
-les 17 et 18 novembre 2024 à Kairouan. Cette mission est liée à des_x000D_
-activités en cours qui nécessitent vraiment une présence sur place, et je_x000D_
-souhaite m'assurer que tout se passe dans les meilleures conditions._x000D_
+Je me permets de vous adresser la présente afin de solliciter une_x000D_
+autorisation d'absence pour des raisons personnelles._x000D_
 _x000D_
-Voici mes informations pour la demande : je m'appelle Imen Souissi, vous_x000D_
-pouvez me joindre à l'adresse imen.souissi@hrtech-solutions.tn, et la_x000D_
-destination est Kairouan pour ces deux journées. L'accord de mon_x000D_
-responsable est encore en attente, mais je souhaitais vous transmettre_x000D_
-cette demande en avance afin d'éviter tout délai de traitement._x000D_
+• Type d'autorisation : Autorisation de sortie exceptionnelle_x000D_
+• Date de l'absence : 27/05/2026_x000D_
+• Heure de départ : 10h00_x000D_
+• Heure de retour : 13h30_x000D_
+• Nombre d'heures : 3h30_x000D_
+• Motif de l'absence : Rendez-vous médical spécialisé ne pouvant être_x000D_
+reporté_x000D_
 _x000D_
-Si vous avez besoin de quoi que ce soit de ma part — documents_x000D_
-supplémentaires, détails sur les objectifs de la mission, ou autre —_x000D_
-n'hésitez pas à me le faire savoir et je vous fournirai tout cela dans les_x000D_
-plus brefs délais._x000D_
+Je m'engage à assurer la continuité de mes tâches en amont et à rattraper_x000D_
+le temps d'absence si cela s'avère nécessaire._x000D_
 _x000D_
-Merci beaucoup pour votre aide et votre disponibilité !_x000D_
+Dans l'attente de votre accord, je reste disponible pour tout échange à ce_x000D_
+sujet._x000D_
 _x000D_
 Cordialement,_x000D_
-yessine haj taieb</t>
+_x000D_
+Ahmed Ben Salem_x000D_
+Développeur Full Stack – Département Informatique_x000D_
+a.bensalem@entreprise.tn | +216 55 000 123</t>
   </si>
   <si>
     <t>Rapport.pdf; Asset 11.png</t>
@@ -432,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -454,7 +665,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -465,7 +676,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -476,15 +687,47 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>3</v>
+      <c r="A5">
+        <v>30</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
